--- a/terceiroSemestre/algebraLinear/ESCALONAMENTO.xlsx
+++ b/terceiroSemestre/algebraLinear/ESCALONAMENTO.xlsx
@@ -46,10 +46,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="# ?/?"/>
-    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -137,40 +136,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -520,16 +523,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>0</v>
@@ -537,23 +540,23 @@
       <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="3" t="e">
+      <c r="H1" s="6" t="n">
         <f aca="false">(D9-B9*H2 -C9*H3)/A1</f>
-        <v>#DIV/0!</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>2</v>
@@ -561,23 +564,23 @@
       <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="e">
+      <c r="H2" s="6" t="n">
         <f aca="false">(D10-C10*H3)/B10</f>
-        <v>#DIV/0!</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>3</v>
@@ -585,27 +588,27 @@
       <c r="G3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="3" t="e">
+      <c r="H3" s="6" t="n">
         <f aca="false">D11/C11</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <f aca="false">A1</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="n">
         <f aca="false">B1</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
         <f aca="false">C1</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="2" t="n">
         <f aca="false">D1</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -616,15 +619,15 @@
       </c>
       <c r="B6" s="1" t="n">
         <f aca="false">-A2*B1+A1*B2</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
         <f aca="false">-A2*C1+A1*C2</f>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="n">
         <f aca="false">-A2*D1+A1*D2</f>
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,34 +637,34 @@
       </c>
       <c r="B7" s="1" t="n">
         <f aca="false">-A3*B1+A1*B3</f>
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="n">
         <f aca="false">-A3*C1+A1*C3</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
         <f aca="false">-A3*D1+A1*D3</f>
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H7" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <f aca="false">A5</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="n">
         <f aca="false">B5</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="n">
         <f aca="false">C5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="n">
         <f aca="false">D5</f>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -671,15 +674,15 @@
       </c>
       <c r="B10" s="1" t="n">
         <f aca="false">B6</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="1" t="n">
         <f aca="false">C6</f>
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">D6</f>
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -693,11 +696,11 @@
       </c>
       <c r="C11" s="1" t="n">
         <f aca="false">-B7*C6+B6*C7</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2" t="n">
         <f aca="false">-B7*D6+B6*D7</f>
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -735,13 +738,13 @@
       <c r="E1" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="7" t="n">
+      <c r="I1" s="8" t="n">
         <f aca="false">(E16-D16*I4-C16*I3-B16*I2)/A16</f>
         <v>1</v>
       </c>
@@ -762,13 +765,13 @@
       <c r="E2" s="2" t="n">
         <v>-1</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" s="8" t="n">
         <f aca="false">(E17-D17*I4-C17*I3)/B17</f>
         <v>0</v>
       </c>
@@ -789,13 +792,13 @@
       <c r="E3" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="I3" s="8" t="n">
         <f aca="false">(E18-D18*I4)/C18</f>
         <v>1</v>
       </c>
@@ -816,13 +819,13 @@
       <c r="E4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="7" t="n">
+      <c r="I4" s="8" t="n">
         <f aca="false">E19/D19</f>
         <v>1</v>
       </c>
